--- a/stories/arbres/TREE-SEC-021.xlsx
+++ b/stories/arbres/TREE-SEC-021.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Hugo est avec maman, dans la chambre. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo écoute maman. Hugo entend les mots : espace montré, adulte voit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers Tom. La couverture est douce. maman sourit. Ici, c'est Tom. Ce n'est pas comme les autres endroits. Hugo se souvient : espace montré, adulte voit. Voici le geste : jouer là où l'adulte a dit. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers Tom. La couverture est douce. maman sourit. Ici, c'est Tom. Ce n'est pas comme les autres endroits. Hugo se souvient : espace montré, adulte voit. Voici le geste : jouer là où l'adulte a dit. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers Tom. La couverture est douce. maman sourit. Ici, c'est Tom. Ce n'est pas comme les autres endroits. Hugo se souvient : espace montré, adulte voit. Voici le geste : jouer là où l'adulte a dit. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Jouer là où l'adulte peut voir.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer là où l'adulte a dit. Hugo respire. Hugo retient : espace montré, adulte voit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2230,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2397,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les cubes. Ça sent le pain chaud. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2588,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2697,6 +2755,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint une pomme. Une feuille tombe. On souffle doucement. Cette fin-là est celle de Tom, les cubes et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un yaourt. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de Tom, les cubes et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un morceau de pain. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de Tom, les cubes et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le livre. Le vent est doux. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3948,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4017,6 +4115,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint une pomme. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de Tom, le livre et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un yaourt. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de Tom, le livre et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un morceau de pain. La lumière est claire. On attend son tour. Cette fin-là est celle de Tom, le livre et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5117,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi la dînette. Le sol est un peu froid. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5308,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5337,6 +5475,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint une pomme. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de Tom, la dînette et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5642,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5661,6 +5809,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un yaourt. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de Tom, la dînette et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5976,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5985,6 +6143,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un morceau de pain. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de Tom, la dînette et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6310,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6171,7 +6339,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers Léa. On entend un oiseau. maman sourit. Ici, c'est Léa. Ce n'est pas comme les autres endroits. Hugo se souvient : espace montré, adulte voit. Voici le geste : jouer là où l'adulte a dit. On écoute jusqu'au bout. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers Léa. On entend un oiseau. maman sourit. Ici, c'est Léa. Ce n'est pas comme les autres endroits. Hugo se souvient : espace montré, adulte voit. Voici le geste : jouer là où l'adulte a dit. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6309,6 +6477,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers Léa. On entend un oiseau. maman sourit. Ici, c'est Léa. Ce n'est pas comme les autres endroits. Hugo se souvient : espace montré, adulte voit. Voici le geste : jouer là où l'adulte a dit. On écoute jusqu'au bout.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6663,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Jouer là où l'adulte peut voir.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6836,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer là où l'adulte a dit. Hugo respire. Hugo retient : espace montré, adulte voit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7027,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7194,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7191,6 +7385,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7353,6 +7552,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint une pomme. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de Léa, les cubes et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7515,6 +7719,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7677,6 +7886,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un yaourt. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de Léa, les cubes et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7839,6 +8053,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8001,6 +8220,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un morceau de pain. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de Léa, les cubes et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8163,6 +8387,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8325,6 +8554,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8511,6 +8745,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8673,6 +8912,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint une pomme. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de Léa, le livre et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9079,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8997,6 +9246,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un yaourt. La lumière est claire. On attend son tour. Cette fin-là est celle de Léa, le livre et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9413,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9321,6 +9580,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un morceau de pain. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de Léa, le livre et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9747,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9914,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9831,6 +10105,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9993,6 +10272,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint une pomme. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de Léa, la dînette et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10155,6 +10439,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10317,6 +10606,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un yaourt. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de Léa, la dînette et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10479,6 +10773,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10641,6 +10940,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un morceau de pain. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de Léa, la dînette et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10803,6 +11107,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10827,7 +11136,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers Sami. Ça sent le pain chaud. maman sourit. Ici, c'est Sami. Ce n'est pas comme les autres endroits. Hugo se souvient : espace montré, adulte voit. Voici le geste : jouer là où l'adulte a dit. On attend son tour. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers Sami. Ça sent le pain chaud. maman sourit. Ici, c'est Sami. Ce n'est pas comme les autres endroits. Hugo se souvient : espace montré, adulte voit. Voici le geste : jouer là où l'adulte a dit. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10965,6 +11274,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers Sami. Ça sent le pain chaud. maman sourit. Ici, c'est Sami. Ce n'est pas comme les autres endroits. Hugo se souvient : espace montré, adulte voit. Voici le geste : jouer là où l'adulte a dit. On attend son tour.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11145,6 +11460,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Jouer là où l'adulte peut voir.</t>
         </is>
       </c>
     </row>
@@ -11313,6 +11633,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer là où l'adulte a dit. Hugo respire. Hugo retient : espace montré, adulte voit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11499,6 +11824,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11661,6 +11991,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11847,6 +12182,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12009,6 +12349,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint une pomme. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de Sami, les cubes et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12171,6 +12516,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12333,6 +12683,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un yaourt. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de Sami, les cubes et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12495,6 +12850,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12657,6 +13017,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un morceau de pain. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de Sami, les cubes et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12819,6 +13184,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12981,6 +13351,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13167,6 +13542,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13329,6 +13709,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint une pomme. La lumière est claire. On attend son tour. Cette fin-là est celle de Sami, le livre et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13491,6 +13876,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13653,6 +14043,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un yaourt. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de Sami, le livre et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13815,6 +14210,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13977,6 +14377,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un morceau de pain. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de Sami, le livre et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14139,6 +14544,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14301,6 +14711,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14487,6 +14902,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14649,6 +15069,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint une pomme. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de Sami, la dînette et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14811,6 +15236,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14973,6 +15403,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un yaourt. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de Sami, la dînette et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15135,6 +15570,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15297,6 +15737,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint un morceau de pain. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de Sami, la dînette et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15459,6 +15904,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15477,7 +15927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15494,6 +15944,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-021.xlsx
+++ b/stories/arbres/TREE-SEC-021.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Hugo est avec maman, dans la chambre. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo écoute maman. Hugo entend les mots : espace montré, adulte voit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Jouer là où l'adulte peut voir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2044,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : jouer là où l'adulte a dit. Hugo respire. Hugo retient : espace montré, adulte voit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2235,6 +2245,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2402,6 +2413,7 @@
           <t>narrateur|Hugo a choisi les cubes. Ça sent le pain chaud. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Hugo rejoint une pomme. Une feuille tombe. On souffle doucement. Cette fin-là est celle de Tom, les cubes et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Hugo rejoint un yaourt. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de Tom, les cubes et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Hugo rejoint un morceau de pain. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de Tom, les cubes et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
           <t>narrateur|Hugo a choisi le livre. Le vent est doux. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3953,6 +3973,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
           <t>narrateur|Hugo rejoint une pomme. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de Tom, le livre et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Hugo rejoint un yaourt. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de Tom, le livre et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Hugo rejoint un morceau de pain. La lumière est claire. On attend son tour. Cette fin-là est celle de Tom, le livre et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|Hugo a choisi la dînette. Le sol est un peu froid. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5313,6 +5341,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5480,6 +5509,7 @@
           <t>narrateur|Hugo rejoint une pomme. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de Tom, la dînette et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5647,6 +5677,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5814,6 +5845,7 @@
           <t>narrateur|Hugo rejoint un yaourt. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de Tom, la dînette et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5981,6 +6013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6148,6 +6181,7 @@
           <t>narrateur|Hugo rejoint un morceau de pain. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de Tom, la dînette et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6315,6 +6349,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6483,6 +6518,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6670,6 +6706,7 @@
           <t>narrateur|Que fait-on ? Jouer là où l'adulte peut voir.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6841,6 +6878,7 @@
           <t>narrateur|Oui. Voici le geste : jouer là où l'adulte a dit. Hugo respire. Hugo retient : espace montré, adulte voit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7032,6 +7070,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7199,6 +7238,7 @@
           <t>narrateur|Hugo a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7390,6 +7430,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7557,6 +7598,7 @@
           <t>narrateur|Hugo rejoint une pomme. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de Léa, les cubes et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7724,6 +7766,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7891,6 +7934,7 @@
           <t>narrateur|Hugo rejoint un yaourt. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de Léa, les cubes et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8058,6 +8102,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8225,6 +8270,7 @@
           <t>narrateur|Hugo rejoint un morceau de pain. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de Léa, les cubes et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8392,6 +8438,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8559,6 +8606,7 @@
           <t>narrateur|Hugo a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8750,6 +8798,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8917,6 +8966,7 @@
           <t>narrateur|Hugo rejoint une pomme. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de Léa, le livre et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9084,6 +9134,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9251,6 +9302,7 @@
           <t>narrateur|Hugo rejoint un yaourt. La lumière est claire. On attend son tour. Cette fin-là est celle de Léa, le livre et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9418,6 +9470,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9585,6 +9638,7 @@
           <t>narrateur|Hugo rejoint un morceau de pain. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de Léa, le livre et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9752,6 +9806,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9919,6 +9974,7 @@
           <t>narrateur|Hugo a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10110,6 +10166,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10277,6 +10334,7 @@
           <t>narrateur|Hugo rejoint une pomme. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de Léa, la dînette et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10444,6 +10502,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10611,6 +10670,7 @@
           <t>narrateur|Hugo rejoint un yaourt. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de Léa, la dînette et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10778,6 +10838,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10945,6 +11006,7 @@
           <t>narrateur|Hugo rejoint un morceau de pain. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de Léa, la dînette et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11112,6 +11174,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11280,6 +11343,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11467,6 +11531,7 @@
           <t>narrateur|Que fait-on ? Jouer là où l'adulte peut voir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11638,6 +11703,7 @@
           <t>narrateur|Oui. Voici le geste : jouer là où l'adulte a dit. Hugo respire. Hugo retient : espace montré, adulte voit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11829,6 +11895,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11996,6 +12063,7 @@
           <t>narrateur|Hugo a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12187,6 +12255,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12354,6 +12423,7 @@
           <t>narrateur|Hugo rejoint une pomme. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de Sami, les cubes et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12521,6 +12591,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12688,6 +12759,7 @@
           <t>narrateur|Hugo rejoint un yaourt. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de Sami, les cubes et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12855,6 +12927,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13022,6 +13095,7 @@
           <t>narrateur|Hugo rejoint un morceau de pain. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de Sami, les cubes et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13189,6 +13263,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13356,6 +13431,7 @@
           <t>narrateur|Hugo a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13547,6 +13623,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13714,6 +13791,7 @@
           <t>narrateur|Hugo rejoint une pomme. La lumière est claire. On attend son tour. Cette fin-là est celle de Sami, le livre et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13881,6 +13959,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14048,6 +14127,7 @@
           <t>narrateur|Hugo rejoint un yaourt. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de Sami, le livre et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14215,6 +14295,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14382,6 +14463,7 @@
           <t>narrateur|Hugo rejoint un morceau de pain. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de Sami, le livre et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14549,6 +14631,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14716,6 +14799,7 @@
           <t>narrateur|Hugo a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : jouer là où l'adulte a dit. Hugo répète tout bas : espace montré, adulte voit. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14907,6 +14991,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15074,6 +15159,7 @@
           <t>narrateur|Hugo rejoint une pomme. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de Sami, la dînette et une pomme. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15241,6 +15327,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15408,6 +15495,7 @@
           <t>narrateur|Hugo rejoint un yaourt. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de Sami, la dînette et un yaourt. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15575,6 +15663,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15742,6 +15831,7 @@
           <t>narrateur|Hugo rejoint un morceau de pain. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de Sami, la dînette et un morceau de pain. Hugo a appris : Jouer là où l'adulte peut voir. Voici le geste : jouer là où l'adulte a dit. Hugo a entendu : espace montré, adulte voit. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15909,6 +15999,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15927,7 +16018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15951,6 +16042,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15965,7 +16070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16152,6 +16257,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
